--- a/artfynd/A 41584-2025 artfynd.xlsx
+++ b/artfynd/A 41584-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1037,6 +1037,224 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128760461</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58546</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gröndalen, Gröndalen, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>543487</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6446726</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tjärstad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128760411</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91239</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gröndalen, Gröndalen, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>543487</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6446726</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tjärstad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41584-2025 artfynd.xlsx
+++ b/artfynd/A 41584-2025 artfynd.xlsx
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128760461</v>
+        <v>128760411</v>
       </c>
       <c r="B5" t="n">
-        <v>58546</v>
+        <v>91239</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,28 +1050,24 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208250</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gröndalen, Gröndalen, Ög</t>
@@ -1113,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128760411</v>
+        <v>128760461</v>
       </c>
       <c r="B6" t="n">
-        <v>91239</v>
+        <v>58546</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,24 +1157,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>208250</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gröndalen, Gröndalen, Ög</t>
@@ -1220,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1230,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,6 +1252,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41584-2025 artfynd.xlsx
+++ b/artfynd/A 41584-2025 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>128760411</v>
       </c>
       <c r="B5" t="n">
-        <v>91239</v>
+        <v>91240</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 41584-2025 artfynd.xlsx
+++ b/artfynd/A 41584-2025 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>128760411</v>
       </c>
       <c r="B5" t="n">
-        <v>91240</v>
+        <v>91267</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>128760461</v>
       </c>
       <c r="B6" t="n">
-        <v>58546</v>
+        <v>58573</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41584-2025 artfynd.xlsx
+++ b/artfynd/A 41584-2025 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>128760411</v>
       </c>
       <c r="B5" t="n">
-        <v>91267</v>
+        <v>91272</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 41584-2025 artfynd.xlsx
+++ b/artfynd/A 41584-2025 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>128760411</v>
       </c>
       <c r="B5" t="n">
-        <v>91272</v>
+        <v>91277</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 41584-2025 artfynd.xlsx
+++ b/artfynd/A 41584-2025 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>128760411</v>
       </c>
       <c r="B5" t="n">
-        <v>91277</v>
+        <v>91281</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>128760461</v>
       </c>
       <c r="B6" t="n">
-        <v>58573</v>
+        <v>58577</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41584-2025 artfynd.xlsx
+++ b/artfynd/A 41584-2025 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>128760411</v>
       </c>
       <c r="B5" t="n">
-        <v>91281</v>
+        <v>91286</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>128760461</v>
       </c>
       <c r="B6" t="n">
-        <v>58577</v>
+        <v>58580</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41584-2025 artfynd.xlsx
+++ b/artfynd/A 41584-2025 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>128760411</v>
       </c>
       <c r="B5" t="n">
-        <v>91293</v>
+        <v>91296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 41584-2025 artfynd.xlsx
+++ b/artfynd/A 41584-2025 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>128760411</v>
       </c>
       <c r="B5" t="n">
-        <v>91296</v>
+        <v>91299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 41584-2025 artfynd.xlsx
+++ b/artfynd/A 41584-2025 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>128760411</v>
       </c>
       <c r="B5" t="n">
-        <v>91299</v>
+        <v>91305</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>128760461</v>
       </c>
       <c r="B6" t="n">
-        <v>58580</v>
+        <v>58582</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>128907509</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 41584-2025 artfynd.xlsx
+++ b/artfynd/A 41584-2025 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>128760411</v>
       </c>
       <c r="B5" t="n">
-        <v>91305</v>
+        <v>91314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>128760461</v>
       </c>
       <c r="B6" t="n">
-        <v>58582</v>
+        <v>58584</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>128907509</v>
       </c>
       <c r="B7" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
